--- a/reports/Debug-snowbowl-20251216/For Winter Ending (Actual)_Budget.xlsx
+++ b/reports/Debug-snowbowl-20251216/For Winter Ending (Actual)_Budget.xlsx
@@ -133,6 +133,120 @@
     <t>HR</t>
   </si>
   <si>
+    <t>D1000</t>
+  </si>
+  <si>
+    <t>Mountain G&amp;A</t>
+  </si>
+  <si>
+    <t>D4032</t>
+  </si>
+  <si>
+    <t>Hart Prairie Retail</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>Resort Services G&amp;A</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>99100</t>
+  </si>
+  <si>
+    <t>Daily Winter Ticketed</t>
+  </si>
+  <si>
+    <t>D2000</t>
+  </si>
+  <si>
+    <t>Ski School</t>
+  </si>
+  <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>Rentals</t>
+  </si>
+  <si>
+    <t>D6030</t>
+  </si>
+  <si>
+    <t>Base Camp Hotel</t>
+  </si>
+  <si>
+    <t>D7010</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>Snowmaking</t>
+  </si>
+  <si>
+    <t>D4031</t>
+  </si>
+  <si>
+    <t>Agassiz Retail</t>
+  </si>
+  <si>
+    <t>D4034</t>
+  </si>
+  <si>
+    <t>Fort Valley Lodge</t>
+  </si>
+  <si>
+    <t>D5113</t>
+  </si>
+  <si>
+    <t>Fremont Restaurant</t>
+  </si>
+  <si>
+    <t>D6740</t>
+  </si>
+  <si>
+    <t>Janitorial</t>
+  </si>
+  <si>
+    <t>99200</t>
+  </si>
+  <si>
+    <t>Winter Season Pass Visits  - Home Resort</t>
+  </si>
+  <si>
+    <t>D5111</t>
+  </si>
+  <si>
+    <t>Hart Prairie Restaurant</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
+    <t>Risk Management</t>
+  </si>
+  <si>
     <t>D3050</t>
   </si>
   <si>
@@ -155,120 +269,6 @@
   </si>
   <si>
     <t>Grounds Maintenance</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>Snowmaking</t>
-  </si>
-  <si>
-    <t>D4031</t>
-  </si>
-  <si>
-    <t>Agassiz Retail</t>
-  </si>
-  <si>
-    <t>D4034</t>
-  </si>
-  <si>
-    <t>Fort Valley Lodge</t>
-  </si>
-  <si>
-    <t>D5113</t>
-  </si>
-  <si>
-    <t>Fremont Restaurant</t>
-  </si>
-  <si>
-    <t>D6740</t>
-  </si>
-  <si>
-    <t>Janitorial</t>
-  </si>
-  <si>
-    <t>99200</t>
-  </si>
-  <si>
-    <t>Winter Season Pass Visits  - Home Resort</t>
-  </si>
-  <si>
-    <t>D5111</t>
-  </si>
-  <si>
-    <t>Hart Prairie Restaurant</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
-    <t>Risk Management</t>
-  </si>
-  <si>
-    <t>99100</t>
-  </si>
-  <si>
-    <t>Daily Winter Ticketed</t>
-  </si>
-  <si>
-    <t>D2000</t>
-  </si>
-  <si>
-    <t>Ski School</t>
-  </si>
-  <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>Rentals</t>
-  </si>
-  <si>
-    <t>D6030</t>
-  </si>
-  <si>
-    <t>Base Camp Hotel</t>
-  </si>
-  <si>
-    <t>D7010</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>D8020</t>
-  </si>
-  <si>
-    <t>Accounting</t>
-  </si>
-  <si>
-    <t>D1000</t>
-  </si>
-  <si>
-    <t>Mountain G&amp;A</t>
-  </si>
-  <si>
-    <t>D4032</t>
-  </si>
-  <si>
-    <t>Hart Prairie Retail</t>
-  </si>
-  <si>
-    <t>D6700</t>
-  </si>
-  <si>
-    <t>Resort Services G&amp;A</t>
-  </si>
-  <si>
-    <t>D6730</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>D6790</t>
-  </si>
-  <si>
-    <t>Transportation</t>
   </si>
 </sst>
 </file>
@@ -914,7 +914,7 @@
         <v>5</v>
       </c>
       <c r="C20" s="2">
-        <v>13573.80</v>
+        <v>41939.12</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>40</v>
@@ -922,16 +922,16 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C21" s="2">
-        <v>18814.00</v>
+        <v>22162.38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -939,10 +939,10 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C22" s="2">
-        <v>41735.52</v>
+        <v>204693.23</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>42</v>
@@ -950,408 +950,408 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C23" s="2">
-        <v>140810.40</v>
+        <v>11502.76</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="2">
-        <v>17124.17</v>
+        <v>17211.51</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C25" s="2">
-        <v>41143.86</v>
+        <v>13787.37</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C26" s="2">
-        <v>12853.54</v>
+        <v>19200.00</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="2">
-        <v>117395.28</v>
+        <v>105188.80</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2">
-        <v>20568.89</v>
+        <v>180389.00</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C29" s="2">
-        <v>4736.16</v>
+        <v>402646.00</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C30" s="2">
-        <v>3414.21</v>
+        <v>48976.12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="2">
-        <v>7107.00</v>
+        <v>25006.24</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C32" s="2">
-        <v>3921.81</v>
+        <v>66932.58</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2">
-        <v>0.00</v>
+        <v>25084.30</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C34" s="2">
-        <v>21897.85</v>
+        <v>39788.06</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2">
-        <v>15825.00</v>
+        <v>117395.28</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C36" s="2">
-        <v>48945.95</v>
+        <v>20568.89</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C37" s="2">
-        <v>268958.08</v>
+        <v>4736.16</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C38" s="2">
-        <v>6641.48</v>
+        <v>3414.21</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C39" s="2">
-        <v>19200.00</v>
+        <v>7107.00</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="2">
-        <v>105188.80</v>
+        <v>3921.81</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C41" s="2">
-        <v>180389.00</v>
+        <v>0.00</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C42" s="2">
-        <v>402646.00</v>
+        <v>21897.85</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C43" s="2">
-        <v>48976.12</v>
+        <v>15825.00</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="2">
-        <v>25006.24</v>
+        <v>48945.95</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C45" s="2">
-        <v>66932.58</v>
+        <v>268958.08</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C46" s="2">
-        <v>25084.30</v>
+        <v>6641.48</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C47" s="2">
-        <v>39788.06</v>
+        <v>13573.80</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C48" s="2">
-        <v>41939.12</v>
+        <v>18814.00</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C49" s="2">
-        <v>22162.38</v>
+        <v>41735.52</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C50" s="2">
-        <v>204693.23</v>
+        <v>140810.40</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C51" s="2">
-        <v>11502.76</v>
+        <v>17124.17</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1359,10 +1359,10 @@
         <v>81</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C52" s="2">
-        <v>17211.51</v>
+        <v>41143.86</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>82</v>
@@ -1376,7 +1376,7 @@
         <v>5</v>
       </c>
       <c r="C53" s="2">
-        <v>13787.37</v>
+        <v>12853.54</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>84</v>
